--- a/DOCS/archipelago_logic.xlsx
+++ b/DOCS/archipelago_logic.xlsx
@@ -8423,7 +8423,7 @@
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Late</t>
+          <t xml:space="preserve">Endgame</t>
         </is>
       </c>
       <c r="G171" s="9"/>
@@ -8461,7 +8461,7 @@
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Late</t>
+          <t xml:space="preserve">Endgame</t>
         </is>
       </c>
       <c r="G172" s="9"/>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Late</t>
+          <t xml:space="preserve">Endgame</t>
         </is>
       </c>
       <c r="G173" s="9"/>
@@ -8537,7 +8537,7 @@
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Late</t>
+          <t xml:space="preserve">Endgame</t>
         </is>
       </c>
       <c r="G174" s="9"/>

--- a/DOCS/archipelago_logic.xlsx
+++ b/DOCS/archipelago_logic.xlsx
@@ -12790,7 +12790,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">(OptionFilter(MammonPortal, 0) &amp; Has("Eletale's Book")) | (OptionFilter(MammonPortal, 1) &amp; ALL_BOSSES_BEATEN) | (OptionFilter(MammonPortal, 2) &amp; ALL_MONSTER_AREAS) | (OptionFilter(MammonPortal, 3) &amp; ALL_BOSSES_BEATEN &amp; ALL_MONSTER_AREAS)</t>
+          <t xml:space="preserve">(OptionFilter(MammonPortal, 0) &amp; Has("Eletale's Book")) | (OptionFilter(MammonPortal, 1) &amp; ALL_BOSSES_BEATEN) | (OptionFilter(MammonPortal, 2) &amp; ALL_MONSTER_AREAS) | (OptionFilter(MammonPortal, 3) &amp; ALL_BOSSES_BEATEN &amp; ALL_MONSTER_AREAS) | (OptionFilter(MammonPortal, 4) &amp; True_()) | (OptionFilter(MammonPortal, 5) &amp; ALL_BOSSES_BEATEN) | (OptionFilter(MammonPortal, 7) &amp; ALL_BOSSES_BEATEN &amp; ALL_MONSTER_AREAS)</t>
         </is>
       </c>
       <c r="C10" s="7">
@@ -12798,7 +12798,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">The way into Mammon's World: the Book in the vanilla game, the portal condition otherwise (the Book is then not in the pool at all).</t>
+          <t xml:space="preserve">The way into Mammon's World: the Book in the vanilla game, the portal condition otherwise (the Book is then not in the pool at all). Portals 4, 5 and 7 also want pages_required Torn Pages, which the generator adds in set_rules: a count from an option cannot be written here.</t>
         </is>
       </c>
     </row>
@@ -14285,12 +14285,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">vanilla 0, all_bosses 1, all_monsters 2, both 3</t>
+          <t xml:space="preserve">vanilla 0, all_bosses 1, all_monsters 2, both 3, all_pages 4, bosses_and_pages 5, bosses_monsters_pages 7</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">What opens Mammon's World: ENDGAME_DOOR. Also makes the Book's Shannon a check and takes the Book out of the pool.</t>
+          <t xml:space="preserve">What opens Mammon's World: ENDGAME_DOOR (a bitmask: 1 bosses, 2 monsters, 4 pages; pages need goal mammon). Also makes the Book's Shannon a check and takes the Book out of the pool.</t>
         </is>
       </c>
       <c r="E4" s="5"/>

--- a/DOCS/archipelago_logic.xlsx
+++ b/DOCS/archipelago_logic.xlsx
@@ -396,7 +396,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Has("Earth Orb") | OptionFilter(BossSouls, 1, operator="ge")</t>
+          <t xml:space="preserve">Has("Earth Orb") | OptionFilter(OpenWorld, 1)</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Melrode and everything open from the start: Holy Plains, Connor Forest, the spirits, the gift NPCs.</t>
+          <t xml:space="preserve">Melrode and everything open from the start: Holy Plains, Connor Forest, Dondoran.</t>
         </is>
       </c>
       <c r="C5" s="7">
@@ -589,7 +589,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">What opens once the first gems are in: Dondoran, Glencoe, West Carmaugh.</t>
+          <t xml:space="preserve">Behind nothing, like the Overworld; no check is put here now (see region_for_stage).</t>
         </is>
       </c>
       <c r="C7" s="7">
@@ -608,7 +608,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zelse (Windward Forest). Behind the Earth Orb.</t>
+          <t xml:space="preserve">Zelse (Windward Forest), and every check of story stage 1. Behind the Earth Orb.</t>
         </is>
       </c>
       <c r="C8" s="7">
@@ -646,7 +646,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isle of Skye, Baragoon Tunnel, Dindom Dries. Behind the Wind Jade.</t>
+          <t xml:space="preserve">Story stage 2: Larapool, Blue Cave, Isle of Skye. Behind the Wind Jade.</t>
         </is>
       </c>
       <c r="C10" s="7">
@@ -665,7 +665,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shilf (Baragoon Tunnel). Behind the Water Jewel.</t>
+          <t xml:space="preserve">Shilf (Baragoon Tunnel), and every check of story stages 3-4: Limelin, Baragoon Tunnel, Dindom Dries, Shamwood, Boil Hole. Behind the Water Jewel.</t>
         </is>
       </c>
       <c r="C11" s="7">
@@ -703,7 +703,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baragoon Moor, Brannoch Castle. Behind the Fire Ruby.</t>
+          <t xml:space="preserve">Story stage 5: Baragoon Moor, Brannoch, Brannoch Castle. Behind the Fire Ruby.</t>
         </is>
       </c>
       <c r="C13" s="7">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Has("Dark Gaol Key")</t>
+          <t xml:space="preserve">DARK_GAOL_KEY</t>
         </is>
       </c>
       <c r="E19" s="5"/>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G4" s="9"/>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G15" s="9"/>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G16" s="9"/>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G17" s="9"/>
@@ -2647,7 +2647,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Mid</t>
         </is>
       </c>
       <c r="G19" s="9"/>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G20" s="9"/>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G21" s="9"/>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G22" s="9"/>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G23" s="9"/>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G24" s="9"/>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G25" s="9"/>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G26" s="9"/>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G27" s="9"/>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G28" s="9"/>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G29" s="9"/>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G30" s="9"/>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G31" s="9"/>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G32" s="9"/>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G33" s="9"/>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G34" s="9"/>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G41" s="9"/>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G42" s="9"/>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G43" s="9"/>
@@ -3597,7 +3597,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G44" s="9"/>
@@ -3635,7 +3635,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G45" s="9"/>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G46" s="9"/>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G47" s="9"/>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G48" s="9"/>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G49" s="9"/>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G50" s="9"/>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Mid</t>
         </is>
       </c>
       <c r="G51" s="9"/>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Mid</t>
         </is>
       </c>
       <c r="G52" s="9"/>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Mid</t>
         </is>
       </c>
       <c r="G53" s="9"/>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Mid</t>
         </is>
       </c>
       <c r="G54" s="9"/>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Mid</t>
         </is>
       </c>
       <c r="G55" s="9"/>
@@ -4053,7 +4053,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Mid</t>
         </is>
       </c>
       <c r="G56" s="9"/>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G57" s="9"/>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G58" s="9"/>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G59" s="9"/>
@@ -4205,7 +4205,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G60" s="9"/>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G61" s="9"/>
@@ -4281,7 +4281,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G62" s="9"/>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G63" s="9"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G64" s="9"/>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G65" s="9"/>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G66" s="9"/>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G67" s="9"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G68" s="9"/>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G69" s="9"/>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G70" s="9"/>
@@ -4623,7 +4623,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G71" s="9"/>
@@ -4661,7 +4661,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G72" s="9"/>
@@ -5307,7 +5307,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G89" s="9"/>
@@ -5345,7 +5345,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G90" s="9"/>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G91" s="9"/>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Mid</t>
         </is>
       </c>
       <c r="G95" s="9"/>
@@ -5573,7 +5573,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G96" s="9"/>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G97" s="9"/>
@@ -5649,7 +5649,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Late</t>
         </is>
       </c>
       <c r="G98" s="9"/>
@@ -5687,7 +5687,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Mid</t>
         </is>
       </c>
       <c r="G99" s="9"/>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Mid</t>
         </is>
       </c>
       <c r="G104" s="9"/>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G105" s="9"/>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G106" s="9"/>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Late</t>
         </is>
       </c>
       <c r="G107" s="9"/>
@@ -6295,7 +6295,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Mid</t>
         </is>
       </c>
       <c r="G115" s="9"/>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Mid</t>
         </is>
       </c>
       <c r="G116" s="9"/>
@@ -6371,7 +6371,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Mid</t>
         </is>
       </c>
       <c r="G117" s="9"/>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Mid</t>
         </is>
       </c>
       <c r="G118" s="9"/>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Mid</t>
         </is>
       </c>
       <c r="G119" s="9"/>
@@ -6485,7 +6485,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G120" s="9"/>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G121" s="9"/>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G122" s="9"/>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G123" s="9"/>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G124" s="9"/>
@@ -6865,7 +6865,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G130" s="9"/>
@@ -6903,7 +6903,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G131" s="9"/>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G132" s="9"/>
@@ -6979,7 +6979,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G133" s="9"/>
@@ -7017,7 +7017,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G134" s="9"/>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G136" s="9"/>
@@ -7207,7 +7207,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G139" s="9"/>
@@ -7245,7 +7245,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G140" s="9"/>
@@ -7283,7 +7283,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G141" s="9"/>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G142" s="9"/>
@@ -7359,7 +7359,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G143" s="9"/>
@@ -7397,7 +7397,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G144" s="9"/>
@@ -7435,7 +7435,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G145" s="9"/>
@@ -7473,7 +7473,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G146" s="9"/>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G147" s="9"/>
@@ -7549,7 +7549,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G148" s="9"/>
@@ -7587,7 +7587,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G149" s="9"/>
@@ -7739,7 +7739,7 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G153" s="9"/>
@@ -7777,7 +7777,7 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G154" s="9"/>
@@ -7815,7 +7815,7 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G155" s="9"/>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G156" s="9"/>
@@ -7967,7 +7967,7 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G159" s="9"/>
@@ -8005,7 +8005,7 @@
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G160" s="9"/>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G161" s="9"/>
@@ -8081,7 +8081,7 @@
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G162" s="9"/>
@@ -8119,7 +8119,7 @@
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G163" s="9"/>
@@ -8157,7 +8157,7 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G164" s="9"/>
@@ -8195,7 +8195,7 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G165" s="9"/>
@@ -8233,7 +8233,7 @@
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G166" s="9"/>
@@ -8347,7 +8347,7 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G169" s="9"/>
@@ -8385,7 +8385,7 @@
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mid</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G170" s="9"/>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G188" s="9"/>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G189" s="9"/>
@@ -9177,7 +9177,7 @@
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G190" s="9"/>
@@ -9215,7 +9215,7 @@
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Mid</t>
         </is>
       </c>
       <c r="G191" s="9"/>
@@ -9253,7 +9253,7 @@
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Mid</t>
         </is>
       </c>
       <c r="G192" s="9"/>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Mid</t>
         </is>
       </c>
       <c r="G193" s="9"/>
@@ -9329,7 +9329,7 @@
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Mid</t>
         </is>
       </c>
       <c r="G194" s="9"/>
@@ -9367,7 +9367,7 @@
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Mid</t>
         </is>
       </c>
       <c r="G195" s="9"/>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Mid</t>
         </is>
       </c>
       <c r="G196" s="9"/>
@@ -9443,7 +9443,7 @@
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G197" s="9"/>
@@ -9481,7 +9481,7 @@
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G198" s="9"/>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G199" s="9"/>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G200" s="9"/>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G201" s="9"/>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G202" s="9"/>
@@ -9671,7 +9671,7 @@
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G203" s="9"/>
@@ -9709,7 +9709,7 @@
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G204" s="9"/>
@@ -9747,7 +9747,7 @@
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G205" s="9"/>
@@ -9785,7 +9785,7 @@
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G206" s="9"/>
@@ -9823,7 +9823,7 @@
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G207" s="9"/>
@@ -9861,7 +9861,7 @@
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G208" s="9"/>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G209" s="9"/>
@@ -9937,7 +9937,7 @@
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G210" s="9"/>
@@ -9975,7 +9975,7 @@
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G211" s="9"/>
@@ -10013,7 +10013,7 @@
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G212" s="9"/>
@@ -10051,7 +10051,7 @@
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G213" s="9"/>
@@ -10089,7 +10089,7 @@
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G214" s="9"/>
@@ -10127,7 +10127,7 @@
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G215" s="9"/>
@@ -10165,7 +10165,7 @@
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G216" s="9"/>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G217" s="9"/>
@@ -10241,7 +10241,7 @@
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G218" s="9"/>
@@ -10279,7 +10279,7 @@
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Late</t>
         </is>
       </c>
       <c r="G219" s="9"/>
@@ -10317,7 +10317,7 @@
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Late</t>
         </is>
       </c>
       <c r="G220" s="9"/>
@@ -10355,7 +10355,7 @@
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Late</t>
         </is>
       </c>
       <c r="G221" s="9"/>
@@ -10393,7 +10393,7 @@
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Late</t>
         </is>
       </c>
       <c r="G222" s="9"/>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Late</t>
         </is>
       </c>
       <c r="G223" s="9"/>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Mid</t>
         </is>
       </c>
       <c r="G224" s="9"/>
@@ -10507,7 +10507,7 @@
       </c>
       <c r="F225" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Mid</t>
         </is>
       </c>
       <c r="G225" s="9"/>
@@ -10545,7 +10545,7 @@
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Mid</t>
         </is>
       </c>
       <c r="G226" s="9"/>
@@ -10583,7 +10583,7 @@
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Mid</t>
         </is>
       </c>
       <c r="G227" s="9"/>
@@ -10621,7 +10621,7 @@
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Mid</t>
         </is>
       </c>
       <c r="G228" s="9"/>
@@ -10659,7 +10659,7 @@
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Mid</t>
         </is>
       </c>
       <c r="G229" s="9"/>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Mid</t>
         </is>
       </c>
       <c r="G230" s="9"/>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Mid</t>
         </is>
       </c>
       <c r="G231" s="9"/>
@@ -10773,7 +10773,7 @@
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Mid</t>
         </is>
       </c>
       <c r="G232" s="9"/>
@@ -10811,7 +10811,7 @@
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Mid</t>
         </is>
       </c>
       <c r="G233" s="9"/>
@@ -10849,7 +10849,7 @@
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Mid</t>
         </is>
       </c>
       <c r="G234" s="9"/>
@@ -10887,7 +10887,7 @@
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G235" s="9"/>
@@ -10925,7 +10925,7 @@
       </c>
       <c r="F236" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G236" s="9"/>
@@ -10963,7 +10963,7 @@
       </c>
       <c r="F237" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G237" s="9"/>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="F238" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G238" s="9"/>
@@ -11039,7 +11039,7 @@
       </c>
       <c r="F239" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G239" s="9"/>
@@ -11077,7 +11077,7 @@
       </c>
       <c r="F240" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G240" s="9"/>
@@ -11115,7 +11115,7 @@
       </c>
       <c r="F241" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G241" s="9"/>
@@ -11153,7 +11153,7 @@
       </c>
       <c r="F242" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G242" s="9"/>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="F243" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G243" s="9"/>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="F244" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Late</t>
         </is>
       </c>
       <c r="G244" s="9"/>
@@ -11267,7 +11267,7 @@
       </c>
       <c r="F245" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Late</t>
         </is>
       </c>
       <c r="G245" s="9"/>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="F251" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G251" s="9"/>
@@ -11533,7 +11533,7 @@
       </c>
       <c r="F252" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G252" s="9"/>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="F253" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G253" s="9"/>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="F254" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G254" s="9"/>
@@ -11647,7 +11647,7 @@
       </c>
       <c r="F255" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G255" s="9"/>
@@ -11685,7 +11685,7 @@
       </c>
       <c r="F256" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G256" s="9"/>
@@ -11723,7 +11723,7 @@
       </c>
       <c r="F257" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G257" s="9"/>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="F258" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G258" s="9"/>
@@ -11799,7 +11799,7 @@
       </c>
       <c r="F259" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G259" s="9"/>
@@ -11837,7 +11837,7 @@
       </c>
       <c r="F260" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G260" s="9"/>
@@ -11875,7 +11875,7 @@
       </c>
       <c r="F261" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G261" s="9"/>
@@ -11913,7 +11913,7 @@
       </c>
       <c r="F262" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 2</t>
         </is>
       </c>
       <c r="G262" s="9"/>
@@ -11989,7 +11989,7 @@
       </c>
       <c r="F264" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G264" s="9"/>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="F265" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G265" s="9"/>
@@ -12065,7 +12065,7 @@
       </c>
       <c r="F266" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G266" s="9"/>
@@ -12103,7 +12103,7 @@
       </c>
       <c r="F267" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G267" s="9"/>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="F268" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G268" s="9"/>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="F269" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G269" s="9"/>
@@ -12217,7 +12217,7 @@
       </c>
       <c r="F270" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Late</t>
         </is>
       </c>
       <c r="G270" s="9"/>
@@ -12255,7 +12255,7 @@
       </c>
       <c r="F271" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Late</t>
         </is>
       </c>
       <c r="G271" s="9"/>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="F272" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G272" s="9"/>
@@ -12331,7 +12331,7 @@
       </c>
       <c r="F273" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G273" s="9"/>
@@ -12369,7 +12369,7 @@
       </c>
       <c r="F274" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G274" s="9"/>
@@ -12407,7 +12407,7 @@
       </c>
       <c r="F275" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G275" s="9"/>
@@ -12445,7 +12445,7 @@
       </c>
       <c r="F276" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G276" s="9"/>
@@ -12483,7 +12483,7 @@
       </c>
       <c r="F277" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Boss 4</t>
         </is>
       </c>
       <c r="G277" s="9"/>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="F278" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Late</t>
         </is>
       </c>
       <c r="G278" s="9"/>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="F279" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Late</t>
         </is>
       </c>
       <c r="G279" s="9"/>
@@ -12597,7 +12597,7 @@
       </c>
       <c r="F280" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overworld</t>
+          <t xml:space="preserve">Late</t>
         </is>
       </c>
       <c r="G280" s="9"/>
@@ -12670,7 +12670,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Has("Earth Orb") | OptionFilter(BossSouls, 1, operator="ge")</t>
+          <t xml:space="preserve">Has("Earth Orb") | Has("Progressive Boss Item", 1) | (CanReachLocation("Boss - Solvaring") &amp; OptionFilter(OpenWorld, 1) &amp; OptionFilter(BossSouls, 1, operator="ge"))</t>
         </is>
       </c>
       <c r="C4" s="7">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">With Boss Souls on, a boss may not be there to drop his gem, so the game opens the gem locks and the gem stops gating anything.</t>
+          <t xml:space="preserve">The gem, or the first Progressive Boss Item (boss_items progressive). With open_world the door is open whatever you hold, but the logic still follows the story: with Boss Souls the way on counts as open once the boss who drops the gem (Solvaring) can be beaten - his Soul is in - and without them it still asks for the gem. Otherwise Brannoch Castle was sphere 1.</t>
         </is>
       </c>
     </row>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Has("Wind Jade") | OptionFilter(BossSouls, 1, operator="ge")</t>
+          <t xml:space="preserve">Has("Wind Jade") | Has("Progressive Boss Item", 2) | (CanReachLocation("Boss - Zelse") &amp; OptionFilter(OpenWorld, 1) &amp; OptionFilter(BossSouls, 1, operator="ge"))</t>
         </is>
       </c>
       <c r="C5" s="7">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">As EARTH_ORB_GATE.</t>
+          <t xml:space="preserve">As EARTH_ORB_GATE; the second Progressive Boss Item, Zelse.</t>
         </is>
       </c>
     </row>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Has("Water Jewel") | OptionFilter(BossSouls, 1, operator="ge")</t>
+          <t xml:space="preserve">Has("Water Jewel") | Has("Progressive Boss Item", 3) | (CanReachLocation("Boss - Nepty") &amp; OptionFilter(OpenWorld, 1) &amp; OptionFilter(BossSouls, 1, operator="ge"))</t>
         </is>
       </c>
       <c r="C6" s="7">
@@ -12718,7 +12718,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">As EARTH_ORB_GATE.</t>
+          <t xml:space="preserve">As EARTH_ORB_GATE; the third, Nepty.</t>
         </is>
       </c>
     </row>
@@ -12730,7 +12730,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Has("Fire Ruby") | OptionFilter(BossSouls, 1, operator="ge")</t>
+          <t xml:space="preserve">Has("Fire Ruby") | Has("Progressive Boss Item", 4) | (CanReachLocation("Boss - Fargo") &amp; OptionFilter(OpenWorld, 1) &amp; OptionFilter(BossSouls, 1, operator="ge"))</t>
         </is>
       </c>
       <c r="C7" s="7">
@@ -12738,19 +12738,19 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">As EARTH_ORB_GATE.</t>
+          <t xml:space="preserve">As EARTH_ORB_GATE; the fourth, Fargo (who drops the Fire Ruby).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALL_BOSSES_BEATEN</t>
+          <t xml:space="preserve">ELETALE_BOOK</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">CanReachLocation("Boss - Solvaring") &amp; CanReachLocation("Boss - Zelse") &amp; CanReachLocation("Boss - Nepty") &amp; CanReachLocation("Boss - Shilf") &amp; CanReachLocation("Boss - Fargo") &amp; CanReachLocation("Boss - Guilty") &amp; CanReachLocation("Boss - Beigis")</t>
+          <t xml:space="preserve">Has("Eletale's Book") | Has("Progressive Boss Item", 5)</t>
         </is>
       </c>
       <c r="C8" s="7">
@@ -12758,19 +12758,19 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">mammon_portal all_bosses: the seven bosses before Mammon. Each boss's own rule already asks for his Soul.</t>
+          <t xml:space="preserve">The Book, or the fifth Progressive Boss Item. Only asked for with mammon_portal vanilla, when the Book is fifth in the progressive order.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALL_MONSTER_AREAS</t>
+          <t xml:space="preserve">DARK_GAOL_KEY</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">CanReachRegion("Overworld") &amp; CanReachRegion("Early") &amp; CanReachRegion("Mid") &amp; CanReachRegion("Late")</t>
+          <t xml:space="preserve">Has("Dark Gaol Key") | (OptionFilter(MammonPortal, 0) &amp; Has("Progressive Boss Item", 6)) | (OptionFilter(MammonPortal, 0, operator="ne") &amp; Has("Progressive Boss Item", 5))</t>
         </is>
       </c>
       <c r="C9" s="7">
@@ -12778,19 +12778,19 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">mammon_portal all_monsters: every region a monster lives in.</t>
+          <t xml:space="preserve">The key, or the last Progressive Boss Item: the sixth, or the fifth when a mammon_portal condition has taken the Book out of the game.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENDGAME_DOOR</t>
+          <t xml:space="preserve">ALL_BOSSES_BEATEN</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">(OptionFilter(MammonPortal, 0) &amp; Has("Eletale's Book")) | (OptionFilter(MammonPortal, 1) &amp; ALL_BOSSES_BEATEN) | (OptionFilter(MammonPortal, 2) &amp; ALL_MONSTER_AREAS) | (OptionFilter(MammonPortal, 3) &amp; ALL_BOSSES_BEATEN &amp; ALL_MONSTER_AREAS) | (OptionFilter(MammonPortal, 4) &amp; True_()) | (OptionFilter(MammonPortal, 5) &amp; ALL_BOSSES_BEATEN) | (OptionFilter(MammonPortal, 7) &amp; ALL_BOSSES_BEATEN &amp; ALL_MONSTER_AREAS)</t>
+          <t xml:space="preserve">CanReachLocation("Boss - Solvaring") &amp; CanReachLocation("Boss - Zelse") &amp; CanReachLocation("Boss - Nepty") &amp; CanReachLocation("Boss - Shilf") &amp; CanReachLocation("Boss - Fargo") &amp; CanReachLocation("Boss - Guilty") &amp; CanReachLocation("Boss - Beigis")</t>
         </is>
       </c>
       <c r="C10" s="7">
@@ -12798,25 +12798,49 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">The way into Mammon's World: the Book in the vanilla game, the portal condition otherwise (the Book is then not in the pool at all). Portals 4, 5 and 7 also want pages_required Torn Pages, which the generator adds in set_rules: a count from an option cannot be written here.</t>
+          <t xml:space="preserve">mammon_portal all_bosses: the seven bosses before Mammon. Each boss's own rule already asks for his Soul.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2"/>
-      <c r="B11" s="9"/>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALL_MONSTER_AREAS</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CanReachRegion("Overworld") &amp; CanReachRegion("Early") &amp; CanReachRegion("Mid") &amp; CanReachRegion("Late")</t>
+        </is>
+      </c>
       <c r="C11" s="7">
         <f>IF(A11="","",COUNTIF(Entrances!$D$4:$D$400,"*"&amp;A11&amp;"*")+COUNTIF(Locations!$G$4:$G$400,"*"&amp;A11&amp;"*")+COUNTIF($B$4:$B$400,"*"&amp;A11&amp;"*"))</f>
       </c>
-      <c r="D11" s="5"/>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mammon_portal all_monsters: every region a monster lives in.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="2"/>
-      <c r="B12" s="9"/>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ENDGAME_DOOR</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(OptionFilter(MammonPortal, 0) &amp; ELETALE_BOOK) | (OptionFilter(MammonPortal, 1) &amp; ALL_BOSSES_BEATEN) | (OptionFilter(MammonPortal, 2) &amp; ALL_MONSTER_AREAS) | (OptionFilter(MammonPortal, 3) &amp; ALL_BOSSES_BEATEN &amp; ALL_MONSTER_AREAS) | (OptionFilter(MammonPortal, 4) &amp; True_()) | (OptionFilter(MammonPortal, 5) &amp; ALL_BOSSES_BEATEN) | (OptionFilter(MammonPortal, 7) &amp; ALL_BOSSES_BEATEN &amp; ALL_MONSTER_AREAS)</t>
+        </is>
+      </c>
       <c r="C12" s="7">
         <f>IF(A12="","",COUNTIF(Entrances!$D$4:$D$400,"*"&amp;A12&amp;"*")+COUNTIF(Locations!$G$4:$G$400,"*"&amp;A12&amp;"*")+COUNTIF($B$4:$B$400,"*"&amp;A12&amp;"*"))</f>
       </c>
-      <c r="D12" s="5"/>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The way into Mammon's World: the Book in the vanilla game, the portal condition otherwise (the Book is then not in the pool at all). Portals 4, 5 and 7 also want pages_required Torn Pages, which the generator adds in set_rules: a count from an option cannot be written here.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2"/>
@@ -13041,6 +13065,22 @@
         <f>IF(A40="","",COUNTIF(Entrances!$D$4:$D$400,"*"&amp;A40&amp;"*")+COUNTIF(Locations!$G$4:$G$400,"*"&amp;A40&amp;"*")+COUNTIF($B$4:$B$400,"*"&amp;A40&amp;"*"))</f>
       </c>
       <c r="D40" s="5"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="7">
+        <f>IF(A41="","",COUNTIF(Entrances!$D$4:$D$400,"*"&amp;A41&amp;"*")+COUNTIF(Locations!$G$4:$G$400,"*"&amp;A41&amp;"*")+COUNTIF($B$4:$B$400,"*"&amp;A41&amp;"*"))</f>
+      </c>
+      <c r="D41" s="5"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="7">
+        <f>IF(A42="","",COUNTIF(Entrances!$D$4:$D$400,"*"&amp;A42&amp;"*")+COUNTIF(Locations!$G$4:$G$400,"*"&amp;A42&amp;"*")+COUNTIF($B$4:$B$400,"*"&amp;A42&amp;"*"))</f>
+      </c>
+      <c r="D42" s="5"/>
     </row>
   </sheetData>
 </worksheet>
@@ -14313,7 +14353,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Each boss's check needs his Soul; the gem gates open (the *_GATE rules).</t>
+          <t xml:space="preserve">Each boss's check needs his Soul. Opens nothing else: that is open_world.</t>
         </is>
       </c>
       <c r="E5" s="5"/>
@@ -14321,12 +14361,12 @@
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">shuffle_orbs</t>
+          <t xml:space="preserve">open_world</t>
         </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ShuffleOrbs</t>
+          <t xml:space="preserve">OpenWorld</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -14336,7 +14376,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Off: the six gate items stay at their vanilla checks (locked in pre_fill). No rule changes.</t>
+          <t xml:space="preserve">On: the game opens the doors, boats and teleporters the four gems lock. The logic still follows the story (the *_GATE rules): with boss_souls a gate is met once the boss who drops its gem can be beaten, without them it still wants the gem.</t>
         </is>
       </c>
       <c r="E6" s="5"/>
@@ -14344,22 +14384,22 @@
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">chestsanity</t>
+          <t xml:space="preserve">boss_items</t>
         </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chestsanity</t>
+          <t xml:space="preserve">BossItems</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">off / on</t>
+          <t xml:space="preserve">normal 0, shuffled 1, progressive 2</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Whether chests are locations.</t>
+          <t xml:space="preserve">Normal: the six gate items stay at their vanilla checks (locked in pre_fill). Shuffled: in the pool. Progressive: the pool has one Progressive Boss Item per gate item instead, each the next of Earth Orb, Wind Jade, Water Jewel, Fire Ruby, Eletale's Book (only with mammon_portal vanilla), Dark Gaol Key - which is why the gates also take a count of them.</t>
         </is>
       </c>
       <c r="E7" s="5"/>
@@ -14367,12 +14407,12 @@
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">giftsanity</t>
+          <t xml:space="preserve">chestsanity</t>
         </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Giftsanity</t>
+          <t xml:space="preserve">Chestsanity</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -14382,7 +14422,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Whether gift NPCs are locations.</t>
+          <t xml:space="preserve">Whether chests are locations.</t>
         </is>
       </c>
       <c r="E8" s="5"/>
@@ -14390,12 +14430,12 @@
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemysanity</t>
+          <t xml:space="preserve">giftsanity</t>
         </is>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enemysanity</t>
+          <t xml:space="preserve">Giftsanity</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -14405,7 +14445,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Whether each monster kind is a location.</t>
+          <t xml:space="preserve">Whether gift NPCs are locations.</t>
         </is>
       </c>
       <c r="E9" s="5"/>
@@ -14413,12 +14453,12 @@
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">spiritsanity</t>
+          <t xml:space="preserve">enemysanity</t>
         </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spiritsanity</t>
+          <t xml:space="preserve">Enemysanity</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -14428,7 +14468,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Whether spirits are locations; also makes one Level Up per spirit.</t>
+          <t xml:space="preserve">Whether each monster kind is a location.</t>
         </is>
       </c>
       <c r="E10" s="5"/>
@@ -14436,22 +14476,22 @@
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">extra_level_ups</t>
+          <t xml:space="preserve">spiritsanity</t>
         </is>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ExtraLevelUps</t>
+          <t xml:space="preserve">Spiritsanity</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 - 99</t>
+          <t xml:space="preserve">off / on</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Extra Level Ups in the pool.</t>
+          <t xml:space="preserve">Whether spirits are locations; also makes one Level Up per spirit.</t>
         </is>
       </c>
       <c r="E11" s="5"/>
@@ -14459,22 +14499,22 @@
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">wingsmith_wings</t>
+          <t xml:space="preserve">extra_level_ups</t>
         </is>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">WingsmithWings</t>
+          <t xml:space="preserve">ExtraLevelUps</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">off / on</t>
+          <t xml:space="preserve">0 - 99</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A wingsmith also hands over his wings. No rule changes.</t>
+          <t xml:space="preserve">Extra Level Ups in the pool.</t>
         </is>
       </c>
       <c r="E12" s="5"/>
@@ -14482,22 +14522,22 @@
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">shuffle_boss_order</t>
+          <t xml:space="preserve">wings</t>
         </is>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ShuffleBossOrder</t>
+          <t xml:space="preserve">Wings</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">off / on</t>
+          <t xml:space="preserve">normal 0, shuffled 1, progressive 2</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The game's own setting. Not in the logic today, although it moves which boss stands where - worth a look if bosses get their own regions.</t>
+          <t xml:space="preserve">Normal: the wingsmiths hand over their wings. Shuffled: one of each in the pool, the wingsmiths give only their check. Progressive: six Progressive Wings instead, each the next wing in town order. No rule changes: no rule needs wings.</t>
         </is>
       </c>
       <c r="E13" s="5"/>
@@ -14505,25 +14545,71 @@
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">wings_in_pool</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WingsInPool</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">none 0, one 1, two 2</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Extra copies of each wing in the pool, on top of what wings puts there (as more Progressive Wings when progressive). No rule changes.</t>
+        </is>
+      </c>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shuffle_boss_order</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ShuffleBossOrder</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">off / on</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The game's own setting. Not in the logic today, although it moves which boss stands where - worth a look if bosses get their own regions.</t>
+        </is>
+      </c>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">goal</t>
         </is>
       </c>
-      <c r="B14" s="0" t="inlineStr">
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Goal</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">mammon 0</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">The only goal.</t>
         </is>
       </c>
-      <c r="E14" s="5"/>
+      <c r="E16" s="5"/>
     </row>
   </sheetData>
 </worksheet>

--- a/DOCS/archipelago_logic.xlsx
+++ b/DOCS/archipelago_logic.xlsx
@@ -12830,7 +12830,7 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">(OptionFilter(MammonPortal, 0) &amp; ELETALE_BOOK) | (OptionFilter(MammonPortal, 1) &amp; ALL_BOSSES_BEATEN) | (OptionFilter(MammonPortal, 2) &amp; ALL_MONSTER_AREAS) | (OptionFilter(MammonPortal, 3) &amp; ALL_BOSSES_BEATEN &amp; ALL_MONSTER_AREAS) | (OptionFilter(MammonPortal, 4) &amp; True_()) | (OptionFilter(MammonPortal, 5) &amp; ALL_BOSSES_BEATEN) | (OptionFilter(MammonPortal, 7) &amp; ALL_BOSSES_BEATEN &amp; ALL_MONSTER_AREAS)</t>
+          <t xml:space="preserve">(OptionFilter(MammonPortal, 0) &amp; ELETALE_BOOK) | (OptionFilter(MammonPortal, 1) &amp; ALL_BOSSES_BEATEN) | (OptionFilter(MammonPortal, 2) &amp; ALL_MONSTER_AREAS) | (OptionFilter(MammonPortal, 3) &amp; ALL_BOSSES_BEATEN &amp; ALL_MONSTER_AREAS) | (OptionFilter(MammonPortal, 4) &amp; True_()) | (OptionFilter(MammonPortal, 5) &amp; ALL_BOSSES_BEATEN) | (OptionFilter(MammonPortal, 7) &amp; ALL_BOSSES_BEATEN &amp; ALL_MONSTER_AREAS) | (OptionFilter(MammonPortal, 8) &amp; True_()) | (OptionFilter(MammonPortal, 24) &amp; True_())</t>
         </is>
       </c>
       <c r="C12" s="7">
@@ -12838,7 +12838,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">The way into Mammon's World: the Book in the vanilla game, the portal condition otherwise (the Book is then not in the pool at all). Portals 4, 5 and 7 also want pages_required Torn Pages, which the generator adds in set_rules: a count from an option cannot be written here.</t>
+          <t xml:space="preserve">The way into Mammon's World: the Book in the vanilla game, the portal condition otherwise (the Book is then not in the pool at all). Portals 4, 5 and 7 also want pages_required Torn Pages, and 8 and 24 the orbs (all four, or orbs_required of them), which the generator adds in set_rules: a count from an option cannot be written here.</t>
         </is>
       </c>
     </row>
@@ -14325,12 +14325,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">vanilla 0, all_bosses 1, all_monsters 2, both 3, all_pages 4, bosses_and_pages 5, bosses_monsters_pages 7</t>
+          <t xml:space="preserve">vanilla 0, all_bosses 1, all_monsters 2, both 3, all_pages 4, bosses_and_pages 5, bosses_monsters_pages 7, all_orbs 8, some_orbs 24</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">What opens Mammon's World: ENDGAME_DOOR (a bitmask: 1 bosses, 2 monsters, 4 pages; pages need goal mammon). Also makes the Book's Shannon a check and takes the Book out of the pool.</t>
+          <t xml:space="preserve">What opens Mammon's World: ENDGAME_DOOR (a bitmask: 1 bosses, 2 monsters, 4 pages, 8 orbs, 16 only orbs_required of them; pages need goal mammon). Also makes the Book's Shannon a check and takes the Book out of the pool.</t>
         </is>
       </c>
       <c r="E4" s="5"/>
